--- a/Result/profitability/6180.xlsx
+++ b/Result/profitability/6180.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06874999999999988</v>
+        <v>-0.2787500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>30.9425</v>
+        <v>29.3</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.41</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1162500000000001</v>
+        <v>-0.07625000000000012</v>
       </c>
       <c r="N3" t="n">
-        <v>32.7125</v>
+        <v>32.10875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.48</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09499999999999986</v>
+        <v>-0.1500000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>35.74375000000001</v>
+        <v>34.28625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03000000000000014</v>
+        <v>-0.06125000000000012</v>
       </c>
       <c r="N5" t="n">
-        <v>37.4025</v>
+        <v>36.87375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1912499999999999</v>
+        <v>0.07874999999999986</v>
       </c>
       <c r="N6" t="n">
-        <v>40.76875</v>
+        <v>39.80875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2987499999999998</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>43.645</v>
+        <v>43.4775</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5462499999999999</v>
+        <v>0.3562499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>47.05</v>
+        <v>45.79875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0.73</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4837499999999998</v>
+        <v>0.4837499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>49.4625</v>
@@ -1774,10 +1774,10 @@
         <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4737499999999999</v>
+        <v>0.4737499999999998</v>
       </c>
       <c r="N11" t="n">
-        <v>49.66625000000001</v>
+        <v>49.66625</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>0.06</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4212499999999999</v>
+        <v>0.4212499999999998</v>
       </c>
       <c r="N12" t="n">
         <v>49.42125</v>
@@ -2030,7 +2030,7 @@
         <v>0.41</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4637499999999998</v>
+        <v>0.4637499999999999</v>
       </c>
       <c r="N13" t="n">
         <v>49.74625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6180</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1827</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1446</v>
+      </c>
+      <c r="E75" t="n">
+        <v>381</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-203</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-11.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-28</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-231</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-155</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1400000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.48125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.412698412698413</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-10.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3241580310880828</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1685258964143427</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
